--- a/DOSSIES_MULTIFORMATO/SECT/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SECT/dossie.xlsx
@@ -812,12 +812,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2015NE00107</t>
+          <t>2015NE00109</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>6/2013</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6295.96</v>
+        <v>1090.51</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -842,12 +842,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2015NE00109</t>
+          <t>2015NE00107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1090.51</v>
+        <v>6295.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2017NE00556</t>
+          <t>2017NE00557</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1439.43</v>
+        <v>380.07</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2017NE00557</t>
+          <t>2017NE00556</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>380.07</v>
+        <v>1439.43</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0000287</t>
+          <t>2025NE0000288</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25247.7</v>
+        <v>5568.48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SERVIDORES E LICENÇA DE USO DE VPN NA SECRETARIA DE ESTADO DAS CIDADES E TERRITÓRIOS.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web – GERWEB, para a publicação de info</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025NE0000288</t>
+          <t>2025NE0000287</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5568.48</v>
+        <v>25247.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web – GERWEB, para a publicação de info</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SERVIDORES E LICENÇA DE USO DE VPN NA SECRETARIA DE ESTADO DAS CIDADES E TERRITÓRIOS.</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025NE0000139</t>
+          <t>2025NE0000137</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2/2025</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12623.85</v>
+        <v>9118.35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1115,19 +1115,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SERVIDORES E LICENÇA DE USO DE VPN NA SECRETARIA DE ESTADO DAS CIDADES E TERRITÓRIOS.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025NE0000137</t>
+          <t>2025NE0000139</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9118.35</v>
+        <v>12623.85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SERVIDORES E LICENÇA DE USO DE VPN NA SECRETARIA DE ESTADO DAS CIDADES E TERRITÓRIOS.</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2018NE00431</t>
+          <t>2018NE00429</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>456.94</v>
+        <v>11402.18</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2018NE00429</t>
+          <t>2018NE00431</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11402.18</v>
+        <v>456.94</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023NE00215</t>
+          <t>2023NE0000215</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1313,14 +1313,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hospedagem e VPN</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da Informação, Hospedagem de servidores em infraestrutura virtualizada na Rede do Governo do Estado do Amazonas,1º T.A CT 011/2022, VIGÊN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023NE0000215</t>
+          <t>2023NE00215</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da Informação, Hospedagem de servidores em infraestrutura virtualizada na Rede do Governo do Estado do Amazonas,1º T.A CT 011/2022, VIGÊN</t>
+          <t>Hospedagem e VPN</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2022NE0000443</t>
+          <t>2022NE0000440</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62674.23</v>
+        <v>9463.040000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1425,14 +1425,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE SALDO DO EMPENHO Nº 0149/2022 EM ATENDIMENTO AO DECRETO Nº 46.621 DE 11/11/2022 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUCAÇÃO ORÇAMENTÁRIA, FINANCEIRA E</t>
+          <t>ANULAÇÃO PARCIAL DE SALDO DO EMPENHO Nº 0146/2022 EM ATENDIMENTO AO DECRETO Nº 46.621 DE 11/11/2022 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUCAÇÃO ORÇAMENTÁRIA, FINANCEIRA E</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2022NE0000440</t>
+          <t>2022NE0000443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9463.040000000001</v>
+        <v>62674.23</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE SALDO DO EMPENHO Nº 0146/2022 EM ATENDIMENTO AO DECRETO Nº 46.621 DE 11/11/2022 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUCAÇÃO ORÇAMENTÁRIA, FINANCEIRA E</t>
+          <t>ANULAÇÃO PARCIAL DE SALDO DO EMPENHO Nº 0149/2022 EM ATENDIMENTO AO DECRETO Nº 46.621 DE 11/11/2022 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUCAÇÃO ORÇAMENTÁRIA, FINANCEIRA E</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2023NE00210</t>
+          <t>2023NE0000210</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gestor Web</t>
+          <t xml:space="preserve">Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web) para atender as necessidades desta Secretaria - </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2023NE0000210</t>
+          <t>2023NE00210</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web) para atender as necessidades desta Secretaria - </t>
+          <t>Gestor Web</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025NE0000047</t>
+          <t>2025NE0000049</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4910.32</v>
+        <v>18236.7</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 02.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025NE0000049</t>
+          <t>2025NE0000047</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18236.7</v>
+        <v>4910.32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -1754,10 +1754,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2019NE00165</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>2019NE00166</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1/2017</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>24/06/2019</t>
@@ -1773,21 +1777,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>anulação (descrição incompleta)</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI, COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO, HOSPEDAGEM DE SERVIDORES, CUJA DESCRIÇÃO ESTA CONTIDA NO ANEXO I E II QUE FAZ PARTE INTEGRANTE DE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2019NE00158</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2019NE00160</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>24/06/2019</t>
@@ -1803,19 +1803,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
+          <t>ANULAÇÃO TOTAL NE 158(DESCRIÇÃO INCOMPLETA)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2019NE00156</t>
+          <t>2019NE00161</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>913.88</v>
+        <v>20069.82</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2019NE00161</t>
+          <t>2019NE00156</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>20069.82</v>
+        <v>913.88</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1893,17 +1893,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2019NE00160</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>2019NE00158</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>24/06/2019</t>
@@ -1919,21 +1923,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL NE 158(DESCRIÇÃO INCOMPLETA)</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2019NE00166</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1/2017</t>
-        </is>
-      </c>
+          <t>2019NE00165</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>24/06/2019</t>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI, COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO, HOSPEDAGEM DE SERVIDORES, CUJA DESCRIÇÃO ESTA CONTIDA NO ANEXO I E II QUE FAZ PARTE INTEGRANTE DE</t>
+          <t>anulação (descrição incompleta)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2022NE0000380</t>
+          <t>2022NE0000379</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2365.76</v>
+        <v>7766.15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1975,14 +1975,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víde</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECT.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2022NE0000379</t>
+          <t>2022NE0000380</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7766.15</v>
+        <v>2365.76</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECT.</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víde</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2016NE00254</t>
+          <t>2016NE00256</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2091,24 +2091,28 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº 015/2012</t>
+          <t>4º TERMO ADITIVO AO CT 15/2012</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2016NE00255</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>2016NE00253</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12/2014</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>22/06/2016</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11402.18</v>
+        <v>876.5599999999999</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2117,28 +2121,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL (DESCRIÇÃO RESUMIDA)</t>
+          <t>1º termo aditivo ao contrato nº 012/2014</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2016NE00253</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>12/2014</t>
-        </is>
-      </c>
+          <t>2016NE00255</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>22/06/2016</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>876.5599999999999</v>
+        <v>11402.18</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2147,14 +2147,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1º termo aditivo ao contrato nº 012/2014</t>
+          <t>ANULAÇÃO TOTAL (DESCRIÇÃO RESUMIDA)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2016NE00256</t>
+          <t>2016NE00254</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CT 15/2012</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº 015/2012</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2021NE0000015</t>
+          <t>2021NE0000014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2259,14 +2259,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ANULAÇÃO NE 0014 DATA INCORRETA</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE INFORMAÇÃO REGULARIZAÇÃO FUNDIÁRIA.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2021NE0000014</t>
+          <t>2021NE0000015</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE INFORMAÇÃO REGULARIZAÇÃO FUNDIÁRIA.</t>
+          <t>ANULAÇÃO NE 0014 DATA INCORRETA</t>
         </is>
       </c>
     </row>
@@ -2318,21 +2318,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2018NE00189</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>12/2014</t>
-        </is>
-      </c>
+          <t>2018NE00191</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>21/03/2018</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3067.96</v>
+        <v>39907.63</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2341,14 +2337,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE) REF. AO 3º T.A. CONTRATO N.º 012/2014 - VIGÊNCIA: 01/09/2017 a 31/08/2018</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 190/2018 PARA CORREÇÃO DA NATUREZA DA DESPESAS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2018NE00192</t>
+          <t>2018NE00190</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2371,14 +2367,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CONTRATO DE PRESTAÇÃO DE SERVIÇO DE LINK DE INTERNET PARA ESTA SPF - CONFORME 6º T.A. CONT. N.º 0015/2012 - VIGÊNCIA: 03/09/2017 a 02/09/2018</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE LINK DE INTERNET PARA ESTA SPF - CONFORME 6º T.A. CONT. N.º 0015/2012 - VIGÊNCIA: 03/09/2017 a 02/09/2018</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2018NE00190</t>
+          <t>2018NE00192</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2401,24 +2397,28 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE LINK DE INTERNET PARA ESTA SPF - CONFORME 6º T.A. CONT. N.º 0015/2012 - VIGÊNCIA: 03/09/2017 a 02/09/2018</t>
+          <t>CONTRATO DE PRESTAÇÃO DE SERVIÇO DE LINK DE INTERNET PARA ESTA SPF - CONFORME 6º T.A. CONT. N.º 0015/2012 - VIGÊNCIA: 03/09/2017 a 02/09/2018</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2018NE00191</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>2018NE00189</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12/2014</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>21/03/2018</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>39907.63</v>
+        <v>3067.96</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2427,17 +2427,21 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 190/2018 PARA CORREÇÃO DA NATUREZA DA DESPESAS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE) REF. AO 3º T.A. CONTRATO N.º 012/2014 - VIGÊNCIA: 01/09/2017 a 31/08/2018</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020NE00025</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>2020NE00026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1/2017</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>21/02/2020</t>
@@ -2453,21 +2457,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL NE 24</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE INFORMAÇÃO REGULARIZAÇÃO FUNDIÁRIA.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020NE00026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1/2017</t>
-        </is>
-      </c>
+          <t>2020NE00025</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>21/02/2020</t>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE INFORMAÇÃO REGULARIZAÇÃO FUNDIÁRIA.</t>
+          <t>ANULAÇÃO TOTAL NE 24</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2024NE0000223</t>
+          <t>2024NE0000228</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>48205.62</v>
+        <v>18236.7</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 02.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2024NE0000228</t>
+          <t>2024NE0000223</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>18236.7</v>
+        <v>48205.62</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024NE0000066</t>
+          <t>2024NE0000067</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>48205.62</v>
+        <v>17666.08</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 01.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024NE0000067</t>
+          <t>2024NE0000066</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>17666.08</v>
+        <v>48205.62</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -2962,10 +2962,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2023NE0000317</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>2023NE00317</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1/2023</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>17/07/2023</t>
@@ -2981,21 +2985,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANMISSÃO DE DADOS.</t>
+          <t>Contrato 001/2023 - Internet e Circuito</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2023NE00317</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1/2023</t>
-        </is>
-      </c>
+          <t>2023NE0000317</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>17/07/2023</t>
@@ -3011,24 +3011,28 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contrato 001/2023 - Internet e Circuito</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANMISSÃO DE DADOS.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2022NE0000367</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>2022NE0000369</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>16/11/2022</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4599.1</v>
+        <v>7766.15</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anulação parcial de saldo da N.E 149/2022 para ajuste orçamentário (atender empenho do mês de nov/22, CT:01/2018 e 08/2022 - PRODAM).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECT.</t>
         </is>
       </c>
     </row>
@@ -3074,21 +3078,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2022NE0000369</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2022NE0000367</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>16/11/2022</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7766.15</v>
+        <v>4599.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3097,19 +3097,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECT.</t>
+          <t>Anulação parcial de saldo da N.E 149/2022 para ajuste orçamentário (atender empenho do mês de nov/22, CT:01/2018 e 08/2022 - PRODAM).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025NE0000237</t>
+          <t>2025NE0000235</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5/2025</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5568.48</v>
+        <v>19124.7</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web – GERWEB, para a publicação de info</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025NE0000235</t>
+          <t>2025NE0000237</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>19124.7</v>
+        <v>5568.48</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web – GERWEB, para a publicação de info</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2023NE0000424</t>
+          <t>2023NE0000421</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8833.040000000001</v>
+        <v>2455.16</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3329,19 +3329,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2023NE0000421</t>
+          <t>2023NE0000424</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2455.16</v>
+        <v>8833.040000000001</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3396,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2021NE0000261</t>
+          <t>2021NE0000268</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>26752.28</v>
+        <v>10746.3</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3419,19 +3419,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE N. 167 PARA ATENDER AOS MESES DE SETEMBRO A DEZEMBRO/2021</t>
+          <t>REFORÇO DA NE N. 39</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2021NE0000268</t>
+          <t>2021NE0000261</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10746.3</v>
+        <v>26752.28</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3449,19 +3449,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE N. 39</t>
+          <t>REFORÇO DA NE N. 167 PARA ATENDER AOS MESES DE SETEMBRO A DEZEMBRO/2021</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2024NE0000282</t>
+          <t>2024NE0000280</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>24102.81</v>
+        <v>9118.35</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 02.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3516,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024NE0000280</t>
+          <t>2024NE0000282</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9118.35</v>
+        <v>24102.81</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2022NE0000304</t>
+          <t>2022NE0000302</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4731.52</v>
+        <v>23219.24</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víde</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da Informação, compreendendo os serviços de Hospedagem de servidores em infraestrutura virtualizada na Rede do Governo do Estado do Amazo</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3636,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2022NE0000302</t>
+          <t>2022NE0000304</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>23219.24</v>
+        <v>4731.52</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da Informação, compreendendo os serviços de Hospedagem de servidores em infraestrutura virtualizada na Rede do Governo do Estado do Amazo</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víde</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2018NE00161</t>
+          <t>2018NE00160</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>39907.63</v>
+        <v>3067.96</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3879,14 +3879,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE NOTA DE EMPENHO N.º 066/2018 - REF. A SERVIÇO DE LINK DE INTERNET PARA ATENDER A ORIENTAÇÃO TÉCNICA N.º 12/2018-GINS DE 07/02/2018 - PARA PODER PROVIDENCIAR NOVO EMPENHO COM NOVA NATUR</t>
+          <t>CANCELAMENTO DE NOTA DE EMPENHO N.º 067/2018 - REF. A SERVIÇO DE HOSPEDAGEM DE SITE PARA ATENDER A ORIENTAÇÃO TÉCNICA N.º 12/2018-GINS DE 07/02/2018</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2018NE00160</t>
+          <t>2018NE00161</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3067.96</v>
+        <v>39907.63</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3905,19 +3905,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE NOTA DE EMPENHO N.º 067/2018 - REF. A SERVIÇO DE HOSPEDAGEM DE SITE PARA ATENDER A ORIENTAÇÃO TÉCNICA N.º 12/2018-GINS DE 07/02/2018</t>
+          <t>CANCELAMENTO DE NOTA DE EMPENHO N.º 066/2018 - REF. A SERVIÇO DE LINK DE INTERNET PARA ATENDER A ORIENTAÇÃO TÉCNICA N.º 12/2018-GINS DE 07/02/2018 - PARA PODER PROVIDENCIAR NOVO EMPENHO COM NOVA NATUR</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026NE0000003</t>
+          <t>2026NE0000004</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2/2025</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>50495.4</v>
+        <v>38249.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SERVIDORES E LICENÇA DE USO DE VPN NA SECRETARIA DE ESTADO DAS CIDADES E TERRITÓRIOS.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026NE0000004</t>
+          <t>2026NE0000003</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>38249.4</v>
+        <v>50495.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3995,19 +3995,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SERVIDORES E LICENÇA DE USO DE VPN NA SECRETARIA DE ESTADO DAS CIDADES E TERRITÓRIOS.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2015NE00017</t>
+          <t>2015NE00008</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6/2013</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3271.53</v>
+        <v>1314.84</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4025,19 +4025,19 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Reempenho do 1º TACT nº 006/13 ¿ Contratação de PJ especializada para prestação de serviço de Hospedagem e Manutenção de WEB SITE, para atender as necessidades desta Secretaria conforme Projeto Básico</t>
+          <t>anula empenho valor global incorreto.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2015NE00001</t>
+          <t>2015NE00002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>17072.34</v>
+        <v>1314.84</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>HOSPEDAGEM DO SITE INSTITUCIONAL DA SPF, INCLUINDO A MANUTENÇÃO DO SITE.</t>
         </is>
       </c>
     </row>
@@ -4092,12 +4092,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2015NE00002</t>
+          <t>2015NE00001</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1314.84</v>
+        <v>17072.34</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4115,19 +4115,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HOSPEDAGEM DO SITE INSTITUCIONAL DA SPF, INCLUINDO A MANUTENÇÃO DO SITE.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015NE00016</t>
+          <t>2015NE00013</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3271.53</v>
+        <v>18887.88</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA COMPLEMENTO DE INFORMAÇÕES</t>
+          <t>Reempenho do 2º TA ao CT nº 0003/2012 Celebrado entre a SECTI e a PRODAM S.A., para prestação de acesso a Rede Mundial INTERNET, Banda Larga com velocidade de 2Mbps, através da Rede METRO/MAO. 12 mese</t>
         </is>
       </c>
     </row>
@@ -4182,12 +4182,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2015NE00008</t>
+          <t>2015NE00016</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>6/2013</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1314.84</v>
+        <v>3271.53</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4205,19 +4205,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>anula empenho valor global incorreto.</t>
+          <t>ANULAÇÃO TOTAL PARA COMPLEMENTO DE INFORMAÇÕES</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2015NE00013</t>
+          <t>2015NE00017</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>6/2013</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>18887.88</v>
+        <v>3271.53</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Reempenho do 2º TA ao CT nº 0003/2012 Celebrado entre a SECTI e a PRODAM S.A., para prestação de acesso a Rede Mundial INTERNET, Banda Larga com velocidade de 2Mbps, através da Rede METRO/MAO. 12 mese</t>
+          <t>Reempenho do 1º TACT nº 006/13 ¿ Contratação de PJ especializada para prestação de serviço de Hospedagem e Manutenção de WEB SITE, para atender as necessidades desta Secretaria conforme Projeto Básico</t>
         </is>
       </c>
     </row>
@@ -4332,12 +4332,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2016NE00017</t>
+          <t>2016NE00024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2629.68</v>
+        <v>34206.54</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4355,19 +4355,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1º termo aditivo ao contrato nº 012/2014</t>
+          <t>4º aditivo ct nº 015/2012</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2016NE00024</t>
+          <t>2016NE00017</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>34206.54</v>
+        <v>2629.68</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4385,14 +4385,14 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>4º aditivo ct nº 015/2012</t>
+          <t>1º termo aditivo ao contrato nº 012/2014</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2016NE00367</t>
+          <t>2016NE00345</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>12895.86</v>
+        <v>10340.26</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4411,14 +4411,14 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>anulação total saldo ne</t>
+          <t>ANULAÇÃO PARCIAL DE SALDO</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2016NE00345</t>
+          <t>2016NE00367</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10340.26</v>
+        <v>12895.86</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4437,14 +4437,14 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE SALDO</t>
+          <t>anulação total saldo ne</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2016NE00340</t>
+          <t>2016NE00369</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5454.4</v>
+        <v>6666.66</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>anulação parcial</t>
+          <t>ANULAÇAO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2016NE00369</t>
+          <t>2016NE00340</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6666.66</v>
+        <v>5454.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4489,14 +4489,14 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ANULAÇAO PARCIAL</t>
+          <t>anulação parcial</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2016NE00340</t>
+          <t>2016NE00369</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5454.4</v>
+        <v>6666.66</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>anulação parcial</t>
+          <t>ANULAÇAO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2016NE00369</t>
+          <t>2016NE00340</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6666.66</v>
+        <v>5454.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4541,14 +4541,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ANULAÇAO PARCIAL</t>
+          <t>anulação parcial</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2016NE00367</t>
+          <t>2016NE00345</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>12895.86</v>
+        <v>10340.26</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4567,14 +4567,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>anulação total saldo ne</t>
+          <t>ANULAÇÃO PARCIAL DE SALDO</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2016NE00345</t>
+          <t>2016NE00367</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10340.26</v>
+        <v>12895.86</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE SALDO</t>
+          <t>anulação total saldo ne</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4660,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024NE0000122</t>
+          <t>2024NE0000120</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>50163.54</v>
+        <v>4910.34</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4683,19 +4683,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 02.</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2024NE0000120</t>
+          <t>2024NE0000122</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4910.34</v>
+        <v>50163.54</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 02.</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -4750,12 +4750,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2022NE0000037</t>
+          <t>2022NE0000041</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7164.2</v>
+        <v>26752.28</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4773,19 +4773,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO DE HOSPEDAGEM DE SERVIDORES CUJA DESCRÇÃO ESTA CONTIDA NO ANEXO I E II QUE PASSA A FAZER PARTE INTE</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS ENTRE A CONTRATADA E A CONTRATANTE, POSSIBILITANDO O ACESSO AOS SISTEMAS CONTRATADOS E RESI</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2022NE0000041</t>
+          <t>2022NE0000037</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>26752.28</v>
+        <v>7164.2</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS ENTRE A CONTRATADA E A CONTRATANTE, POSSIBILITANDO O ACESSO AOS SISTEMAS CONTRATADOS E RESI</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO DE HOSPEDAGEM DE SERVIDORES CUJA DESCRÇÃO ESTA CONTIDA NO ANEXO I E II QUE PASSA A FAZER PARTE INTE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2015NE00077</t>
+          <t>2015NE00070</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4829,14 +4829,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014, prestação de serviço de Hospedagem e Manutenção de WEB SITE, meses OUTUBRO E NOVEMBRO/2014</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014. prestação de serviço de Hospedagem e Manutenção de WEB SITE, meses OUTUBRO E NOVEMBRO/2014.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2015NE00081</t>
+          <t>2015NE00064</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1090.51</v>
+        <v>6295.96</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, prestação de serviço de Hospedagem e Manutenção de WEB SITE. DEZEMBRO/2015</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 0209/2014. prestação de acesso a Rede Mundial INTERNET, Banda Larga com velocidade de 2Mbps, através da Rede METRO/MAO. 12 meses; DIRAF n</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2015NE00082</t>
+          <t>2015NE00084</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -4881,14 +4881,14 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE NOTA DE EMPENHO PARA COMPLEMENTO DE INFORMAÇÕES</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014. prestação de serviço de Hospedagem e Manutenção de WEB SITE, meses OUTUBRO E NOVEMBRO/2014.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2015NE00065</t>
+          <t>2015NE00076</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6295.96</v>
+        <v>1090.51</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4907,14 +4907,14 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DE NE PARA COMPLEMENTO DE INFORMAÇÃO</t>
+          <t>ANULAÇÃO DE NOTA DE EMPENHO PARA COMPLEMENTO DE INFORMAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2015NE00080</t>
+          <t>2015NE00066</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2079.54</v>
+        <v>18887.88</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4933,14 +4933,14 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014, prestação de serviço de Hospedagem e Manutenção de WEB SITE. Meses OUTUBRO E NOVEMBRO/2014.</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 0209/2014. prestação de acesso a Rede Mundial INTERNET, Banda Larga com velocidade de 2Mbps, através da Rede METRO/MAO, meses OUTUBRO, NO</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2015NE00075</t>
+          <t>2015NE00078</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2015NE00078</t>
+          <t>2015NE00075</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5018,7 +5018,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2015NE00066</t>
+          <t>2015NE00080</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>18887.88</v>
+        <v>2079.54</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5037,14 +5037,14 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 0209/2014. prestação de acesso a Rede Mundial INTERNET, Banda Larga com velocidade de 2Mbps, através da Rede METRO/MAO, meses OUTUBRO, NO</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014, prestação de serviço de Hospedagem e Manutenção de WEB SITE. Meses OUTUBRO E NOVEMBRO/2014.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2015NE00076</t>
+          <t>2015NE00065</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1090.51</v>
+        <v>6295.96</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5063,14 +5063,14 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE NOTA DE EMPENHO PARA COMPLEMENTO DE INFORMAÇÃO</t>
+          <t>ANULAÇÃO TOTAL DE NE PARA COMPLEMENTO DE INFORMAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2015NE00084</t>
+          <t>2015NE00082</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5089,14 +5089,14 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014. prestação de serviço de Hospedagem e Manutenção de WEB SITE, meses OUTUBRO E NOVEMBRO/2014.</t>
+          <t>ANULAÇÃO DE NOTA DE EMPENHO PARA COMPLEMENTO DE INFORMAÇÕES</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2015NE00064</t>
+          <t>2015NE00081</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>6295.96</v>
+        <v>1090.51</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5115,14 +5115,14 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 0209/2014. prestação de acesso a Rede Mundial INTERNET, Banda Larga com velocidade de 2Mbps, através da Rede METRO/MAO. 12 meses; DIRAF n</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, prestação de serviço de Hospedagem e Manutenção de WEB SITE. DEZEMBRO/2015</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2015NE00070</t>
+          <t>2015NE00077</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5141,19 +5141,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014. prestação de serviço de Hospedagem e Manutenção de WEB SITE, meses OUTUBRO E NOVEMBRO/2014.</t>
+          <t>PAGAMENTO DE DESPESA DE EXERCICIO ANTERIOR, Reempenho da NE nº 025/2014, prestação de serviço de Hospedagem e Manutenção de WEB SITE, meses OUTUBRO E NOVEMBRO/2014</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025NE0000006</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>18236.7</v>
+        <v>4910.32</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5171,19 +5171,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000006</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4910.32</v>
+        <v>18236.7</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5201,21 +5201,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 02.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT. TC: 0001/2023 A</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2024NE0000040</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>11/2022</t>
-        </is>
-      </c>
+          <t>2024NE0000036</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
           <t>02/01/2024</t>
@@ -5231,28 +5227,24 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 01.</t>
+          <t>ANULAÇÃO TOTL DA NE Nº 10/2024 SEM EFETIVAÇÃO DA DESPESA, PARA CORRIGIR O PROGRAMA DE TRABALHO</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2024NE0000042</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>8/2022</t>
-        </is>
-      </c>
+          <t>2024NE0000035</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4910.32</v>
+        <v>17666.08</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5261,24 +5253,28 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
+          <t>ANULAÇÃO TOTL DA NE Nº 08/2024 SEM EFETIVAÇÃO DA DESPESA, PARA CORRIGIR O PROGRAMA DE TRABALHO</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2024NE0000037</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>2024NE0000008</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1/2023</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4910.32</v>
+        <v>17666.08</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5287,19 +5283,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTL DA NE Nº 11/2024 SEM EFETIVAÇÃO DA DESPESA, PARA CORRIGIR O PROGRAMA DE TRABALHO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2024NE0000039</t>
+          <t>2024NE0000011</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5308,7 +5304,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>17666.08</v>
+        <v>4910.32</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5317,19 +5313,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2024NE0000011</t>
+          <t>2024NE0000039</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5338,7 +5334,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4910.32</v>
+        <v>17666.08</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5347,28 +5343,24 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2024NE0000008</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>1/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000037</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>17666.08</v>
+        <v>4910.32</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5377,24 +5369,28 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
+          <t>ANULAÇÃO TOTL DA NE Nº 11/2024 SEM EFETIVAÇÃO DA DESPESA, PARA CORRIGIR O PROGRAMA DE TRABALHO</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024NE0000035</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+          <t>2024NE0000042</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>8/2022</t>
+        </is>
+      </c>
       <c r="C168" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>17666.08</v>
+        <v>4910.32</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5403,17 +5399,21 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTL DA NE Nº 08/2024 SEM EFETIVAÇÃO DA DESPESA, PARA CORRIGIR O PROGRAMA DE TRABALHO</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2024NE0000036</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+          <t>2024NE0000040</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>11/2022</t>
+        </is>
+      </c>
       <c r="C169" t="inlineStr">
         <is>
           <t>02/01/2024</t>
@@ -5429,19 +5429,19 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTL DA NE Nº 10/2024 SEM EFETIVAÇÃO DA DESPESA, PARA CORRIGIR O PROGRAMA DE TRABALHO</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2023NE0000009</t>
+          <t>2023NE0000006</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>92876.96000000001</v>
+        <v>31064.6</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5459,19 +5459,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CT 11/2022-SECT, Contratação de empresa especializada em Serviços de Tecnologia da informação,compreendendo os serviços de Hospedagem de servidores em infraestrutura virtualizada na Rede do Governo do</t>
+          <t>5º T.A AO CT 01/2018 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECT.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2023NE0000006</t>
+          <t>2023NE0000009</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>31064.6</v>
+        <v>92876.96000000001</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5489,19 +5489,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>5º T.A AO CT 01/2018 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECT.</t>
+          <t>CT 11/2022-SECT, Contratação de empresa especializada em Serviços de Tecnologia da informação,compreendendo os serviços de Hospedagem de servidores em infraestrutura virtualizada na Rede do Governo do</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2020NE00002</t>
+          <t>2020NE00003</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5705.52</v>
+        <v>37909.7</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5519,19 +5519,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI, COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO, HOSPEDAGEM DE SERVIDORES, CUJA DESCRIÇÃO ESTA CONTIDA NO ANEXO I E II QUE FAZ PARTE INTEGRANTE DE</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2020NE00003</t>
+          <t>2020NE00002</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>37909.7</v>
+        <v>5705.52</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI, COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO, HOSPEDAGEM DE SERVIDORES, CUJA DESCRIÇÃO ESTA CONTIDA NO ANEXO I E II QUE FAZ PARTE INTEGRANTE DE</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5586,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2018NE00067</t>
+          <t>2018NE00066</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>3506.24</v>
+        <v>45608.72</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5609,19 +5609,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2018NE00066</t>
+          <t>2018NE00067</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>45608.72</v>
+        <v>3506.24</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5639,19 +5639,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2017NE00022</t>
+          <t>2017NE00024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1753.12</v>
+        <v>22804.36</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5669,19 +5669,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE) - 2º T.A. CONT. N.º 012/2014 - VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2017NE00024</t>
+          <t>2017NE00022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>22804.36</v>
+        <v>1753.12</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE) - 2º T.A. CONT. N.º 012/2014 - VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2014NE00036</t>
+          <t>2014NE00025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>6/2013</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>35567.09</v>
+        <v>11437.47</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5759,19 +5759,19 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Contrato No. 3/2012 - Acesso … rede Internet banda de 2 Mbps</t>
+          <t>Contrato No. 6/2013 - Hospedagem de Site</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2014NE00025</t>
+          <t>2014NE00036</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>6/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11437.47</v>
+        <v>35567.09</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5789,19 +5789,19 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Contrato No. 6/2013 - Hospedagem de Site</t>
+          <t>Contrato No. 3/2012 - Acesso … rede Internet banda de 2 Mbps</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2017NE00493</t>
+          <t>2017NE00496</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>5701.09</v>
+        <v>876.5599999999999</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5819,19 +5819,19 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2017NE00496</t>
+          <t>2017NE00493</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>876.5599999999999</v>
+        <v>5701.09</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2015NE00554</t>
+          <t>2015NE00556</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>876.5599999999999</v>
+        <v>2304.69</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2015NE00556</t>
+          <t>2015NE00554</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2304.69</v>
+        <v>876.5599999999999</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5908,12 +5908,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2023NE0000479</t>
+          <t>2023NE0000480</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>17666.08</v>
+        <v>4910.32</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5931,19 +5931,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2023NE0000480</t>
+          <t>2023NE0000479</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4910.32</v>
+        <v>17666.08</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET E TRANSMISSÃO DE DADOS, PARA ATENDER AS NECESSIDADES DESTA SECRETARIA DE ESTADO DAS CIDADAES E TERRITÓRIOS - SECT.</t>
         </is>
       </c>
     </row>
@@ -5994,12 +5994,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2019NE00234</t>
+          <t>2019NE00233</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>20069.82</v>
+        <v>8558.280000000001</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6017,19 +6017,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI, COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO, HOSPEDAGEM DE SERVIDORES, CUJA DESCRIÇÃO ESTA CONTIDA NO ANEXO I E II QUE FAZ PARTE INTEGRANTE DE</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2019NE00233</t>
+          <t>2019NE00234</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>8558.280000000001</v>
+        <v>20069.82</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6047,17 +6047,21 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE INFRAESTRUTURA DE TI, COMPREENDENDO OS SERVIÇOS DE INSTALAÇÃO, HOSPEDAGEM DE SERVIDORES, CUJA DESCRIÇÃO ESTA CONTIDA NO ANEXO I E II QUE FAZ PARTE INTEGRANTE DE</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET POR FIBRA OPTICA COM GARANTIA DE 100% EM DOWLOAD E UPLOAD, CONFORME PROJETO BASICO.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2017NE00388</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
+          <t>2017NE00387</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>12/2014</t>
+        </is>
+      </c>
       <c r="C191" t="inlineStr">
         <is>
           <t>01/09/2017</t>
@@ -6073,19 +6077,19 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE NE PARA CORREÇÃO DE PROCESSO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2017NE00391</t>
+          <t>2017NE00389</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6094,7 +6098,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>876.5599999999999</v>
+        <v>11402.18</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6103,19 +6107,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2017NE00389</t>
+          <t>2017NE00391</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6124,7 +6128,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11402.18</v>
+        <v>876.5599999999999</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6133,21 +6137,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE DISPONIBILIDADE DE ACESSO REMOTO PARA ACESSO AO COMPUTADOR CENTRAL DA CONTRATADA, E A REDE MUNDIAL INTERNET, COM LINK DE 10MBPS E INTERNET DE 3 MBPS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2017NE00387</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>12/2014</t>
-        </is>
-      </c>
+          <t>2017NE00388</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
           <t>01/09/2017</t>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM MANUTENÇÃO DO SITE DA SPF (HOSPEDAGEM DO SITE)</t>
+          <t>ANULAÇÃO DE NE PARA CORREÇÃO DE PROCESSO</t>
         </is>
       </c>
     </row>
@@ -6196,10 +6196,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2016NE00333</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>2016NE00334</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>12/2014</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>01/09/2016</t>
@@ -6215,28 +6219,24 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 0330/2016 PARA CORRIGIR A DESCRIÇÃO DO EMPENHO.</t>
+          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF OBJETIVO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES DO CONTRATO INICIAL. VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2016NE00329</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>15/2012</t>
-        </is>
-      </c>
+          <t>2016NE00333</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
           <t>01/09/2016</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>22804.36</v>
+        <v>1753.12</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6245,19 +6245,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>5º T.A. DO CONTRATO N.º 0015/2012 - VIGÊNCIA: 03/09/2016 a 02/09/2017 - CONTRATAÇÃO DE LINK DE INTERNET</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 0330/2016 PARA CORRIGIR A DESCRIÇÃO DO EMPENHO.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2016NE00330</t>
+          <t>2016NE00329</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1753.12</v>
+        <v>22804.36</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF - VIGÊNCIA: 01/09/2016 a 31/08/2017 - CONTRATAÇÃO PARA MANUTENÇÃO DO SITE DA SPF.</t>
+          <t>5º T.A. DO CONTRATO N.º 0015/2012 - VIGÊNCIA: 03/09/2016 a 02/09/2017 - CONTRATAÇÃO DE LINK DE INTERNET</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2016NE00334</t>
+          <t>2016NE00330</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6305,14 +6305,14 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF OBJETIVO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES DO CONTRATO INICIAL. VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
+          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF - VIGÊNCIA: 01/09/2016 a 31/08/2017 - CONTRATAÇÃO PARA MANUTENÇÃO DO SITE DA SPF.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2016NE00330</t>
+          <t>2016NE00334</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6335,19 +6335,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF - VIGÊNCIA: 01/09/2016 a 31/08/2017 - CONTRATAÇÃO PARA MANUTENÇÃO DO SITE DA SPF.</t>
+          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF OBJETIVO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES DO CONTRATO INICIAL. VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2016NE00329</t>
+          <t>2016NE00330</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>22804.36</v>
+        <v>1753.12</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6365,24 +6365,28 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>5º T.A. DO CONTRATO N.º 0015/2012 - VIGÊNCIA: 03/09/2016 a 02/09/2017 - CONTRATAÇÃO DE LINK DE INTERNET</t>
+          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF - VIGÊNCIA: 01/09/2016 a 31/08/2017 - CONTRATAÇÃO PARA MANUTENÇÃO DO SITE DA SPF.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2016NE00333</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>2016NE00329</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>15/2012</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
           <t>01/09/2016</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1753.12</v>
+        <v>22804.36</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6391,21 +6395,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 0330/2016 PARA CORRIGIR A DESCRIÇÃO DO EMPENHO.</t>
+          <t>5º T.A. DO CONTRATO N.º 0015/2012 - VIGÊNCIA: 03/09/2016 a 02/09/2017 - CONTRATAÇÃO DE LINK DE INTERNET</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2016NE00334</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>12/2014</t>
-        </is>
-      </c>
+          <t>2016NE00333</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
           <t>01/09/2016</t>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2º T.A. DO CONTRATO N.º 012/2014-SPF OBJETIVO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES DO CONTRATO INICIAL. VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 0330/2016 PARA CORRIGIR A DESCRIÇÃO DO EMPENHO.</t>
         </is>
       </c>
     </row>
@@ -6454,12 +6454,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2015NE00432</t>
+          <t>2015NE00436</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1753.12</v>
+        <v>5701.09</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6484,12 +6484,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2015NE00436</t>
+          <t>2015NE00432</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>5701.09</v>
+        <v>1753.12</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6544,12 +6544,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2023NE0000274</t>
+          <t>2023NE0000272</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>24102.81</v>
+        <v>2455.16</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6567,19 +6567,19 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 01.</t>
+          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2023NE0000272</t>
+          <t>2023NE0000274</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2455.16</v>
+        <v>24102.81</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6597,19 +6597,19 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializa em serviços de (Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web-website. TC: 0008/2022 AD: 01.</t>
+          <t>Contratação de empresa especializada em Serviços de Tecnologia da informação, Hospedagem de servidores em infraestrutura virtualizada,Licença de VPN para acesso ao Data Center. TC: 0011/2022 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2017NE00142</t>
+          <t>2017NE00143</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>22804.36</v>
+        <v>1753.12</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6627,19 +6627,19 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE LINK DE INTERNET PARA ATENDER AS NECESSIDADE DA SPF CONF. 5º T.A. DO CONT. N.º 015/2012 VIGÊNCIA: 03/09/2016 a 02/09/2017</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO E HOSPEDAGEM DE SITE DESTA SPF CONF. 2º T.A. DO CONT. N.º 012/2014 - VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2017NE00143</t>
+          <t>2017NE00142</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1753.12</v>
+        <v>22804.36</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO E HOSPEDAGEM DE SITE DESTA SPF CONF. 2º T.A. DO CONT. N.º 012/2014 - VIGÊNCIA: 01/09/2016 a 31/08/2017</t>
+          <t>PRESTAÇÃO DE LINK DE INTERNET PARA ATENDER AS NECESSIDADE DA SPF CONF. 5º T.A. DO CONT. N.º 015/2012 VIGÊNCIA: 03/09/2016 a 02/09/2017</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2015NE00164</t>
+          <t>2015NE00163</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6773,19 +6773,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Cobertura Financeira de abril a agosto/2015</t>
+          <t>aNULAÇÃO DESCRIÇÃO NE 162 INCORRETA</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2015NE00162</t>
+          <t>2015NE00166</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>15/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>28505.45</v>
+        <v>2191.4</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6803,14 +6803,14 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CT 15/2012</t>
+          <t>ct n. 012/2014</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2015NE00157</t>
+          <t>2015NE00161</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6833,14 +6833,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2º termo aditivo ct 15/2012</t>
+          <t>ANULAÇÃO (NATUREZA DE DESPESA INCORRETA)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2015NE00161</t>
+          <t>2015NE00157</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6863,19 +6863,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ANULAÇÃO (NATUREZA DE DESPESA INCORRETA)</t>
+          <t>2º termo aditivo ct 15/2012</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2015NE00166</t>
+          <t>2015NE00162</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>15/2012</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2191.4</v>
+        <v>28505.45</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ct n. 012/2014</t>
+          <t>CT 15/2012</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2015NE00163</t>
+          <t>2015NE00164</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>aNULAÇÃO DESCRIÇÃO NE 162 INCORRETA</t>
+          <t>Cobertura Financeira de abril a agosto/2015</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SECT/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SECT/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-07-31</t>
         </is>
       </c>
     </row>
